--- a/survey_templates/036_pickled_vegetable_export_survey--survey_templates.xlsx
+++ b/survey_templates/036_pickled_vegetable_export_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,9 +441,9 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="45" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -525,13 +525,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>export_survey</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>What is your export survey?</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Please provide a brief description of your export survey.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -548,13 +552,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>destinations</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Which destinations do you export to?</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>List the countries or regions you export to.</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -566,18 +574,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>products</t>
+          <t>export_products</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>export_products</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>What pickled vegetable products do you export?</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Please select the products you export.</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -594,13 +606,13 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>quantity</t>
+          <t>How much do you export per shipment?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -612,18 +624,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>operational_challenges</t>
+          <t>operational_issues</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>operational_challenges</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>Do you face any operational issues?</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Yes or No</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -640,13 +656,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>export_channels</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>Which export channels do you use?</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Please select one export channel.</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -663,13 +683,13 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>export_value</t>
+          <t>What is the export value per shipment?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -681,22 +701,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>destinations</t>
+          <t>exported_to</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>destinations</t>
+          <t>Where do you export?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Where do you export the pickled vegetables?</t>
+          <t>List the countries or regions you export to.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -708,18 +728,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>operational_issues</t>
+          <t>export_issues</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>operational_issues</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>Do you face any export issues?</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Yes or No</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -731,12 +755,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>export_products</t>
+          <t>export_products_2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>export_products</t>
+          <t>Export Products 2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -754,12 +778,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>quantity</t>
+          <t>total_exports</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>quantity</t>
+          <t>How many total exports per shipment?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -780,10 +804,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C33"/>
+  <dimension ref="A1:C39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
   </cols>
@@ -813,12 +837,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>usa</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>USA</t>
         </is>
       </c>
     </row>
@@ -830,520 +854,622 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>mexico</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Mexico</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>products_choices</t>
+          <t>destinations_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>pickled_cucumbers</t>
+          <t>canada</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Pickled Cucumbers</t>
+          <t>Canada</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>products_choices</t>
+          <t>destinations_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>pickled_peppers</t>
+          <t>china</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Pickled Peppers</t>
+          <t>China</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>products_choices</t>
+          <t>destinations_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>pickled_olives</t>
+          <t>japan</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Pickled Olives</t>
+          <t>Japan</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>products_choices</t>
+          <t>destinations_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>pickled_tomatoes</t>
+          <t>korea</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Pickled Tomatoes</t>
+          <t>Korea</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>products_choices</t>
+          <t>destinations_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>pickled_beets</t>
+          <t>europe</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Pickled Beets</t>
+          <t>Europe</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>products_choices</t>
+          <t>destinations_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>pickled_onions</t>
+          <t>other_country</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Pickled Onions</t>
+          <t>Other Country</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>products_choices</t>
+          <t>export_products_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>pickled_carrots</t>
+          <t>pickled_cucumbers</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Pickled Carrots</t>
+          <t>Pickled Cucumbers</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>operational_challenges_choices</t>
+          <t>export_products_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>pickled_peppers</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Pickled Peppers</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>operational_challenges_choices</t>
+          <t>export_products_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>pickled_olives</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Pickled Olives</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>export_channels_choices</t>
+          <t>export_products_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>trade_shows</t>
+          <t>pickled_tomatoes</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Trade Shows</t>
+          <t>Pickled Tomatoes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>export_channels_choices</t>
+          <t>export_products_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>online_marketplaces</t>
+          <t>pickled_beets</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Online Marketplaces</t>
+          <t>Pickled Beets</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>export_channels_choices</t>
+          <t>export_products_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>retailers</t>
+          <t>pickled_onions</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Retailers</t>
+          <t>Pickled Onions</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>export_channels_choices</t>
+          <t>export_products_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>exporters_associations</t>
+          <t>pickled_carrots</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Exporters Associations</t>
+          <t>Pickled Carrots</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>destinations_choices</t>
+          <t>operational_issues_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>usa</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>destinations_choices</t>
+          <t>operational_issues_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>mexico</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>destinations_choices</t>
+          <t>export_channels_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>canada</t>
+          <t>trade_shows</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Trade Shows</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>destinations_choices</t>
+          <t>export_channels_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>china</t>
+          <t>online_marketplaces</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Online Marketplaces</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>destinations_choices</t>
+          <t>export_channels_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>japan</t>
+          <t>retailers</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Retailers</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>destinations_choices</t>
+          <t>export_channels_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>korea</t>
+          <t>exporters_associations</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Korea</t>
+          <t>Exporters Associations</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>destinations_choices</t>
+          <t>exported_to_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>europe</t>
+          <t>usa</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>USA</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>destinations_choices</t>
+          <t>exported_to_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>other_country</t>
+          <t>mexico</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Other Country</t>
+          <t>Mexico</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>operational_issues_choices</t>
+          <t>exported_to_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>canada</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Canada</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>operational_issues_choices</t>
+          <t>exported_to_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>china</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>China</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>export_products_choices</t>
+          <t>exported_to_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>pickled_cucumbers</t>
+          <t>japan</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Pickled Cucumbers</t>
+          <t>Japan</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>export_products_choices</t>
+          <t>exported_to_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>pickled_peppers</t>
+          <t>korea</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Pickled Peppers</t>
+          <t>Korea</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>export_products_choices</t>
+          <t>exported_to_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>pickled_olives</t>
+          <t>europe</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Pickled Olives</t>
+          <t>Europe</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>export_products_choices</t>
+          <t>exported_to_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>pickled_tomatoes</t>
+          <t>other_country</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Pickled Tomatoes</t>
+          <t>Other Country</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>export_products_choices</t>
+          <t>export_issues_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>pickled_beets</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Pickled Beets</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>export_products_choices</t>
+          <t>export_issues_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>pickled_onions</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Pickled Onions</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>export_products_choices</t>
+          <t>export_products_2_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
+          <t>pickled_cucumbers</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Pickled Cucumbers</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>export_products_2_choices</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>pickled_peppers</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Pickled Peppers</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>export_products_2_choices</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>pickled_olives</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Pickled Olives</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>export_products_2_choices</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>pickled_tomatoes</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Pickled Tomatoes</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>export_products_2_choices</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>pickled_beets</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Pickled Beets</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>export_products_2_choices</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>pickled_onions</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Pickled Onions</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>export_products_2_choices</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
           <t>pickled_carrots</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>Pickled Carrots</t>
         </is>
